--- a/reports/빅딜/history/2026-06-18/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-06-18/빅딜_league_mgf_report.xlsx
@@ -11,11 +11,15 @@
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="함몰" sheetId="3" r:id="rId3"/>
     <sheet name="모기가앙해따" sheetId="4" r:id="rId4"/>
+    <sheet name="눈탱이" sheetId="5" r:id="rId5"/>
+    <sheet name="찬밤" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈탱이!$A$1:$J$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">모기가앙해따!$A$1:$J$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">찬밤!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">함몰!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="477">
   <si>
     <t>guild_name</t>
   </si>
@@ -76,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>357</t>
+    <t>347</t>
   </si>
   <si>
     <t>10위</t>
@@ -88,7 +92,7 @@
     <t>28명</t>
   </si>
   <si>
-    <t>2509조 3726억 3577만</t>
+    <t>2632조 1252억 4503만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -160,6 +164,51 @@
     <t>슬블리님</t>
   </si>
   <si>
+    <t>눈탱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%88%88%ED%83%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>30위</t>
+  </si>
+  <si>
+    <t>2397조 739억 5004만</t>
+  </si>
+  <si>
+    <t>적게일하고 많이버는 놈팽이들의 모임. 단톡방 참여 필수, 공헌2500이상,활동 열심히 하실분만 신청주세요 길드문의 : 둘짱</t>
+  </si>
+  <si>
+    <t>완쨩</t>
+  </si>
+  <si>
+    <t>찬밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B0%AC%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>31위</t>
+  </si>
+  <si>
+    <t>2372조 969억 3318만</t>
+  </si>
+  <si>
+    <t>대찬밤</t>
+  </si>
+  <si>
+    <t>겨울수니</t>
+  </si>
+  <si>
     <t>member_rank_in_guild</t>
   </si>
   <si>
@@ -202,7 +251,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>739조 4854억 2432만</t>
+    <t>843조 5952억 4610만</t>
   </si>
   <si>
     <t>2</t>
@@ -220,7 +269,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>307조 7463억 3792만</t>
+    <t>319조 3997억 3984만</t>
   </si>
   <si>
     <t>3</t>
@@ -295,7 +344,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>68조 599억 2945만</t>
+    <t>72조 3325억 7572만</t>
   </si>
   <si>
     <t>8</t>
@@ -325,7 +374,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>55조 6935억 3703만</t>
+    <t>55조 7141억 1314만</t>
   </si>
   <si>
     <t>10</t>
@@ -340,7 +389,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>46조 4727억 3261만</t>
+    <t>47조 329억 9211만</t>
   </si>
   <si>
     <t>11</t>
@@ -436,6 +485,18 @@
     <t>18</t>
   </si>
   <si>
+    <t>홍식</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9D</t>
+  </si>
+  <si>
+    <t>26조 9869억 5188만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>퍼퓸</t>
   </si>
   <si>
@@ -445,19 +506,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>26조 5230억 5725만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>홍식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>26조 2823억 5660만</t>
+    <t>26조 8910억 7821만</t>
   </si>
   <si>
     <t>20</t>
@@ -532,7 +581,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>15조 9426억 2537만</t>
+    <t>15조 9566억 6825만</t>
   </si>
   <si>
     <t>26</t>
@@ -556,7 +605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>13조 2041억 58만</t>
+    <t>13조 2070억 2142만</t>
   </si>
   <si>
     <t>28</t>
@@ -989,6 +1038,426 @@
   </si>
   <si>
     <t>119억 8763만</t>
+  </si>
+  <si>
+    <t>둘짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%98%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>449조 1484억 5159만</t>
+  </si>
+  <si>
+    <t>두바이환불</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EB%B0%94%EC%9D%B4%ED%99%98%EB%B6%88</t>
+  </si>
+  <si>
+    <t>371조 1860억 4857만</t>
+  </si>
+  <si>
+    <t>안산초지동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%82%B0%EC%B4%88%EC%A7%80%EB%8F%99</t>
+  </si>
+  <si>
+    <t>258조 4031억 7171만</t>
+  </si>
+  <si>
+    <t>900원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=900%EC%9B%90</t>
+  </si>
+  <si>
+    <t>204조 2452억 926만</t>
+  </si>
+  <si>
+    <t>나르탕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%A5%B4%ED%83%95</t>
+  </si>
+  <si>
+    <t>193조 4821억 1697만</t>
+  </si>
+  <si>
+    <t>안산중앙동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%82%B0%EC%A4%91%EC%95%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>125조 741억 8617만</t>
+  </si>
+  <si>
+    <t>두바이슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EB%B0%94%EC%9D%B4%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>117조 4864억 3198만</t>
+  </si>
+  <si>
+    <t>동동링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%8F%99%EB%A7%81</t>
+  </si>
+  <si>
+    <t>103조 5357억 3537만</t>
+  </si>
+  <si>
+    <t>우논노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%85%BC%EB%85%B8</t>
+  </si>
+  <si>
+    <t>96조 6144억 3993만</t>
+  </si>
+  <si>
+    <t>롤녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%85%80</t>
+  </si>
+  <si>
+    <t>58조 517억 5758만</t>
+  </si>
+  <si>
+    <t>갑구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%91%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>41조 7861억 8048만</t>
+  </si>
+  <si>
+    <t>mumu5</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=mumu5</t>
+  </si>
+  <si>
+    <t>40조 6208억 1263만</t>
+  </si>
+  <si>
+    <t>짜반</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%B0%98</t>
+  </si>
+  <si>
+    <t>14조 5293억 31만</t>
+  </si>
+  <si>
+    <t>빠이링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EC%9D%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>13조 2869억 3943만</t>
+  </si>
+  <si>
+    <t>창쪼림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%BD%EC%AA%BC%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>8조 6504억 7197만</t>
+  </si>
+  <si>
+    <t>확률단속</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%95%EB%A5%A0%EB%8B%A8%EC%86%8D</t>
+  </si>
+  <si>
+    <t>7조 7023억 931만</t>
+  </si>
+  <si>
+    <t>꼼웅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%BC%EC%9B%85</t>
+  </si>
+  <si>
+    <t>6조 1613억 8314만</t>
+  </si>
+  <si>
+    <t>황금만물</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EB%A7%8C%EB%AC%BC</t>
+  </si>
+  <si>
+    <t>3조 1032억 5231만</t>
+  </si>
+  <si>
+    <t>하리하릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%A6%AC%ED%95%98%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>272조 7941억 5679만</t>
+  </si>
+  <si>
+    <t>게임하다퇴근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%8C%EC%9E%84%ED%95%98%EB%8B%A4%ED%87%B4%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>167조 2551억 1645만</t>
+  </si>
+  <si>
+    <t>잣깐느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A3%EA%B9%90%EB%8A%90</t>
+  </si>
+  <si>
+    <t>167조 2196억 879만</t>
+  </si>
+  <si>
+    <t>쑐쑐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%90%EC%91%90</t>
+  </si>
+  <si>
+    <t>156조 6352억 92만</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Dijon</t>
+  </si>
+  <si>
+    <t>145조 6819억 4812만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EC%88%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>140조 563억 5059만</t>
+  </si>
+  <si>
+    <t>비비쁨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EC%81%A8</t>
+  </si>
+  <si>
+    <t>127조 8287억 68만</t>
+  </si>
+  <si>
+    <t>임주몽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%A3%BC%EB%AA%BD</t>
+  </si>
+  <si>
+    <t>112조 3886억 8328만</t>
+  </si>
+  <si>
+    <t>밍편</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%ED%8E%B8</t>
+  </si>
+  <si>
+    <t>109조 90억 92만</t>
+  </si>
+  <si>
+    <t>베짱짱이기사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EC%A7%B1%EC%A7%B1%EC%9D%B4%EA%B8%B0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>105조 9771억 4620만</t>
+  </si>
+  <si>
+    <t>류츠하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%EC%B8%A0%ED%95%98</t>
+  </si>
+  <si>
+    <t>93조 480억 1812만</t>
+  </si>
+  <si>
+    <t>븁뵵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%81%EB%B5%B5</t>
+  </si>
+  <si>
+    <t>66조 3952억 8931만</t>
+  </si>
+  <si>
+    <t>어허누나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%97%88%EB%88%84%EB%82%98</t>
+  </si>
+  <si>
+    <t>61조 5664억 8592만</t>
+  </si>
+  <si>
+    <t>서아니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%95%84%EB%8B%88</t>
+  </si>
+  <si>
+    <t>61조 106억 4863만</t>
+  </si>
+  <si>
+    <t>투옹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EC%98%B9</t>
+  </si>
+  <si>
+    <t>59조 5828억 3563만</t>
+  </si>
+  <si>
+    <t>hepta</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=hepta</t>
+  </si>
+  <si>
+    <t>52조 6444억 8386만</t>
+  </si>
+  <si>
+    <t>장거반</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EA%B1%B0%EB%B0%98</t>
+  </si>
+  <si>
+    <t>42조 5279억 1693만</t>
+  </si>
+  <si>
+    <t>두팡해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%ED%8C%A1%ED%95%B4</t>
+  </si>
+  <si>
+    <t>38조 7714억 6251만</t>
+  </si>
+  <si>
+    <t>띠띨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%A0%EB%9D%A8</t>
+  </si>
+  <si>
+    <t>37조 4398억 8260만</t>
+  </si>
+  <si>
+    <t>괄사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B4%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>36조 3661억 6761만</t>
+  </si>
+  <si>
+    <t>승우링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%9A%B0%EB%A7%81</t>
+  </si>
+  <si>
+    <t>34조 2655억 48만</t>
+  </si>
+  <si>
+    <t>혜리밍밍밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%A6%AC%EB%B0%8D%EB%B0%8D%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>33조 3728억 5439만</t>
+  </si>
+  <si>
+    <t>하이퍼스타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%ED%8D%BC%EC%8A%A4%ED%83%80</t>
+  </si>
+  <si>
+    <t>31조 5685억 8367만</t>
+  </si>
+  <si>
+    <t>신아리2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%95%84%EB%A6%AC2</t>
+  </si>
+  <si>
+    <t>28조 4611억 5570만</t>
+  </si>
+  <si>
+    <t>약방</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EB%B0%A9</t>
+  </si>
+  <si>
+    <t>28조 272억 6204만</t>
+  </si>
+  <si>
+    <t>초코뭉치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%AD%89%EC%B9%98</t>
+  </si>
+  <si>
+    <t>27조 1290억 9487만</t>
+  </si>
+  <si>
+    <t>비합</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%95%A9</t>
+  </si>
+  <si>
+    <t>21조 2075억 5312만</t>
+  </si>
+  <si>
+    <t>쮸팡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AE%B8%ED%8C%A1</t>
+  </si>
+  <si>
+    <t>18조 6830억 5267만</t>
+  </si>
+  <si>
+    <t>민물꼬기잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%AC%BC%EA%BC%AC%EA%B8%B0%EC%9E%89</t>
+  </si>
+  <si>
+    <t>14조 6007억 3561만</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1531,12 +2000,96 @@
         <v>24</v>
       </c>
     </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M4"/>
+  <autoFilter ref="A1:M6"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1"/>
     <hyperlink ref="B3" r:id="rId2"/>
     <hyperlink ref="B4" r:id="rId3"/>
+    <hyperlink ref="B5" r:id="rId4"/>
+    <hyperlink ref="B6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1561,28 +2114,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -1593,28 +2146,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -1625,28 +2178,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -1657,28 +2210,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -1689,7 +2242,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>23</v>
@@ -1698,19 +2251,19 @@
         <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -1721,28 +2274,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -1753,28 +2306,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -1785,28 +2338,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -1817,28 +2370,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -1849,28 +2402,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -1881,28 +2434,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -1913,28 +2466,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -1945,28 +2498,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -1977,28 +2530,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2009,28 +2562,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2041,28 +2594,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2073,28 +2626,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2105,28 +2658,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2137,28 +2690,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2169,28 +2722,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2201,28 +2754,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -2233,28 +2786,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -2265,28 +2818,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -2297,28 +2850,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -2329,28 +2882,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -2361,28 +2914,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -2393,28 +2946,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -2425,28 +2978,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -2457,28 +3010,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -2540,28 +3093,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2572,7 +3125,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>34</v>
@@ -2581,19 +3134,19 @@
         <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2604,28 +3157,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2636,28 +3189,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2668,28 +3221,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2700,28 +3253,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2732,28 +3285,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2764,28 +3317,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2796,28 +3349,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2828,28 +3381,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2860,28 +3413,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2892,28 +3445,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2924,28 +3477,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2956,28 +3509,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2988,28 +3541,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3020,28 +3573,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3052,28 +3605,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3084,28 +3637,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3116,28 +3669,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3148,28 +3701,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3180,28 +3733,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3212,28 +3765,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3244,28 +3797,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3276,28 +3829,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3308,28 +3861,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3340,28 +3893,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3372,28 +3925,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3404,28 +3957,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3436,28 +3989,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3468,28 +4021,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3500,28 +4053,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3585,28 +4138,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3617,7 +4170,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>44</v>
@@ -3626,19 +4179,19 @@
         <v>44</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3649,28 +4202,28 @@
         <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3681,28 +4234,28 @@
         <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3713,28 +4266,28 @@
         <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3745,28 +4298,28 @@
         <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3777,28 +4330,28 @@
         <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3809,28 +4362,28 @@
         <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3841,28 +4394,28 @@
         <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3873,28 +4426,28 @@
         <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3905,28 +4458,28 @@
         <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>289</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3937,28 +4490,28 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3969,28 +4522,28 @@
         <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4001,28 +4554,28 @@
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4033,28 +4586,28 @@
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4080,4 +4633,1665 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J19"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/reports/빅딜/history/2026-06-18/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-06-18/빅딜_league_mgf_report.xlsx
@@ -16,9 +16,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈탱이!$A$1:$J$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">모기가앙해따!$A$1:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈탱이!$A$1:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">모기가앙해따!$A$1:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">찬밤!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">함몰!$A$1:$J$31</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="468">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>347</t>
+    <t>350</t>
   </si>
   <si>
     <t>10위</t>
@@ -113,7 +113,7 @@
     <t>Scania 36</t>
   </si>
   <si>
-    <t>340</t>
+    <t>341</t>
   </si>
   <si>
     <t>3위</t>
@@ -125,7 +125,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>2740조 5304억 2413만</t>
+    <t>2751조 4544억 7617만</t>
   </si>
   <si>
     <t>미접속 + 길드 콘텐츠 미참여 + 무료 공헌도 미기부 시 추방 / 길톡 운영중 / 문의: 큼직전사(20시 이후)</t>
@@ -143,7 +143,7 @@
     <t>Scania 22</t>
   </si>
   <si>
-    <t>343</t>
+    <t>345</t>
   </si>
   <si>
     <t>7위</t>
@@ -152,10 +152,10 @@
     <t>Lv.7</t>
   </si>
   <si>
-    <t>20명</t>
-  </si>
-  <si>
-    <t>2714조 1503억 7140만</t>
+    <t>19명</t>
+  </si>
+  <si>
+    <t>2693조 1363억 6960만</t>
   </si>
   <si>
     <t>모기가앙해따 많관부^.^</t>
@@ -173,7 +173,7 @@
     <t>Scania 27</t>
   </si>
   <si>
-    <t>370</t>
+    <t>376</t>
   </si>
   <si>
     <t>30위</t>
@@ -194,7 +194,7 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B0%AC%EB%B0%A4</t>
   </si>
   <si>
-    <t>372</t>
+    <t>379</t>
   </si>
   <si>
     <t>31위</t>
@@ -449,426 +449,417 @@
     <t>15</t>
   </si>
   <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>34조 8856억 2109만</t>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>32조 2348억 9606만</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>32조 2348억 9606만</t>
+    <t>정태준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
+  </si>
+  <si>
+    <t>30조 3309억 1252만</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>정태준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
-  </si>
-  <si>
-    <t>30조 3309억 1252만</t>
+    <t>홍식</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9D</t>
+  </si>
+  <si>
+    <t>26조 9869억 5188만</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>홍식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>26조 9869억 5188만</t>
+    <t>퍼퓸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>26조 8910억 7821만</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>퍼퓸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>26조 8910억 7821만</t>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>23조 2903억 7449만</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>23조 2903억 7449만</t>
+    <t>므고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>23조 2054억 8842만</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>므고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>23조 2054억 8842만</t>
+    <t>제스프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>19조 4921억 5164만</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>제스프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>19조 4921억 5164만</t>
+    <t>자유이용껀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>19조 3012억 1344만</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>자유이용껀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>19조 3012억 1344만</t>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>18조 428억 2050만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>18조 428억 2050만</t>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>15조 9566억 6825만</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>15조 9566억 6825만</t>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>15조 2549억 8294만</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>15조 2549억 8294만</t>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>13조 2070억 2142만</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>13조 2070억 2142만</t>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>8조 2619억 4735만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%BC%EC%A7%81%EC%A0%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1707조 7542억 7958만</t>
+  </si>
+  <si>
+    <t>행운크로와상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%96%89%EC%9A%B4%ED%81%AC%EB%A1%9C%EC%99%80%EC%83%81</t>
+  </si>
+  <si>
+    <t>291조 4470억 8282만</t>
+  </si>
+  <si>
+    <t>악긔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B8%94</t>
+  </si>
+  <si>
+    <t>171조 7919억 9161만</t>
+  </si>
+  <si>
+    <t>쓸애긔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%93%B8%EC%95%A0%EA%B8%94</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>134조 6711억 5346만</t>
+  </si>
+  <si>
+    <t>쓰게</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%93%B0%EA%B2%8C</t>
+  </si>
+  <si>
+    <t>77조 6687억 8782만</t>
+  </si>
+  <si>
+    <t>지방도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%B0%A9%EB%8F%84</t>
+  </si>
+  <si>
+    <t>48조 3399억 2301만</t>
+  </si>
+  <si>
+    <t>샷다맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%B7%EB%8B%A4%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>40조 651억 7667만</t>
+  </si>
+  <si>
+    <t>은또링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%98%90%EB%A7%81</t>
+  </si>
+  <si>
+    <t>32조 8611억 8367만</t>
+  </si>
+  <si>
+    <t>무안공항</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%95%88%EA%B3%B5%ED%95%AD</t>
+  </si>
+  <si>
+    <t>30조 775억 7392만</t>
+  </si>
+  <si>
+    <t>파닥닥숭숭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EB%8B%A5%EB%8B%A5%EC%88%AD%EC%88%AD</t>
+  </si>
+  <si>
+    <t>27조 1803억 4688만</t>
+  </si>
+  <si>
+    <t>S2비흔S2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=S2%EB%B9%84%ED%9D%94S2</t>
+  </si>
+  <si>
+    <t>20조 3292억 7979만</t>
+  </si>
+  <si>
+    <t>봄오리1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EC%98%A4%EB%A6%AC1</t>
+  </si>
+  <si>
+    <t>18조 5581억 2327만</t>
+  </si>
+  <si>
+    <t>임프몬젤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%94%84%EB%AA%AC%EC%A0%A4</t>
+  </si>
+  <si>
+    <t>14조 5187억 6034만</t>
+  </si>
+  <si>
+    <t>네핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%ED%95%91</t>
+  </si>
+  <si>
+    <t>13조 3382억 6579만</t>
+  </si>
+  <si>
+    <t>이더5000</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8D%945000</t>
+  </si>
+  <si>
+    <t>12조 407억 5388만</t>
+  </si>
+  <si>
+    <t>웃네</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%83%EB%84%A4</t>
+  </si>
+  <si>
+    <t>11조 9042억 6608만</t>
+  </si>
+  <si>
+    <t>차핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%ED%95%91</t>
+  </si>
+  <si>
+    <t>10조 294억 6526만</t>
+  </si>
+  <si>
+    <t>남궁다은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%EA%B6%81%EB%8B%A4%EC%9D%80</t>
+  </si>
+  <si>
+    <t>9조 1329억 6639만</t>
+  </si>
+  <si>
+    <t>꽃냠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%83%A0</t>
+  </si>
+  <si>
+    <t>8조 7437억 7268만</t>
+  </si>
+  <si>
+    <t>최강다은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EA%B0%95%EB%8B%A4%EC%9D%80</t>
+  </si>
+  <si>
+    <t>8조 3688억 570만</t>
+  </si>
+  <si>
+    <t>환경보호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EA%B2%BD%EB%B3%B4%ED%98%B8</t>
+  </si>
+  <si>
+    <t>7조 8506억 5376만</t>
+  </si>
+  <si>
+    <t>스태틱의단검</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%9C%ED%8B%B1%EC%9D%98%EB%8B%A8%EA%B2%80</t>
+  </si>
+  <si>
+    <t>7조 5637억 146만</t>
+  </si>
+  <si>
+    <t>상급이다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B8%89%EC%9D%B4%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>7조 3720억 2210만</t>
+  </si>
+  <si>
+    <t>삐졌음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%90%EC%A1%8C%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>6조 9069억 7246만</t>
+  </si>
+  <si>
+    <t>성월야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%9B%94%EC%95%BC</t>
+  </si>
+  <si>
+    <t>6조 6783억 7144만</t>
+  </si>
+  <si>
+    <t>알른지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%A5%B8%EC%A7%80</t>
+  </si>
+  <si>
+    <t>6조 5725억 7031만</t>
+  </si>
+  <si>
+    <t>연평후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%ED%8F%89%ED%9B%84</t>
+  </si>
+  <si>
+    <t>6조 2525억 4645만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>8조 2619억 4735만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%BC%EC%A7%81%EC%A0%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1707조 7542억 7958만</t>
-  </si>
-  <si>
-    <t>행운크로와상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%96%89%EC%9A%B4%ED%81%AC%EB%A1%9C%EC%99%80%EC%83%81</t>
-  </si>
-  <si>
-    <t>281조 3274억 6338만</t>
-  </si>
-  <si>
-    <t>악긔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EA%B8%94</t>
-  </si>
-  <si>
-    <t>171조 7919억 9161만</t>
-  </si>
-  <si>
-    <t>쓸애긔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%93%B8%EC%95%A0%EA%B8%94</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>134조 6711억 5346만</t>
-  </si>
-  <si>
-    <t>쓰게</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%93%B0%EA%B2%8C</t>
-  </si>
-  <si>
-    <t>77조 6687억 8782만</t>
-  </si>
-  <si>
-    <t>지방도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%B0%A9%EB%8F%84</t>
-  </si>
-  <si>
-    <t>48조 3399억 2301만</t>
-  </si>
-  <si>
-    <t>샷다맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%B7%EB%8B%A4%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>40조 651억 7667만</t>
-  </si>
-  <si>
-    <t>은또링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%98%90%EB%A7%81</t>
-  </si>
-  <si>
-    <t>32조 8013억 7705만</t>
-  </si>
-  <si>
-    <t>무안공항</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%95%88%EA%B3%B5%ED%95%AD</t>
-  </si>
-  <si>
-    <t>30조 775억 7392만</t>
-  </si>
-  <si>
-    <t>파닥닥숭숭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EB%8B%A5%EB%8B%A5%EC%88%AD%EC%88%AD</t>
-  </si>
-  <si>
-    <t>26조 4357억 2089만</t>
-  </si>
-  <si>
-    <t>S2비흔S2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=S2%EB%B9%84%ED%9D%94S2</t>
-  </si>
-  <si>
-    <t>20조 3292억 7979만</t>
-  </si>
-  <si>
-    <t>봄오리1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EC%98%A4%EB%A6%AC1</t>
-  </si>
-  <si>
-    <t>18조 5581억 2327만</t>
-  </si>
-  <si>
-    <t>임프몬젤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%94%84%EB%AA%AC%EC%A0%A4</t>
-  </si>
-  <si>
-    <t>14조 5187억 6034만</t>
-  </si>
-  <si>
-    <t>네핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%ED%95%91</t>
-  </si>
-  <si>
-    <t>13조 3382억 6579만</t>
-  </si>
-  <si>
-    <t>이더5000</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8D%945000</t>
-  </si>
-  <si>
-    <t>12조 407억 5388만</t>
-  </si>
-  <si>
-    <t>웃네</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%83%EB%84%A4</t>
-  </si>
-  <si>
-    <t>11조 9042억 6608만</t>
-  </si>
-  <si>
-    <t>차핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%ED%95%91</t>
-  </si>
-  <si>
-    <t>10조 294억 6526만</t>
-  </si>
-  <si>
-    <t>남궁다은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%EA%B6%81%EB%8B%A4%EC%9D%80</t>
-  </si>
-  <si>
-    <t>9조 1329억 6639만</t>
-  </si>
-  <si>
-    <t>꽃냠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%83%A0</t>
-  </si>
-  <si>
-    <t>8조 7437억 7268만</t>
-  </si>
-  <si>
-    <t>최강다은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EA%B0%95%EB%8B%A4%EC%9D%80</t>
-  </si>
-  <si>
-    <t>8조 3688억 570만</t>
-  </si>
-  <si>
-    <t>환경보호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EA%B2%BD%EB%B3%B4%ED%98%B8</t>
-  </si>
-  <si>
-    <t>7조 8506억 5376만</t>
-  </si>
-  <si>
-    <t>스태틱의단검</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%9C%ED%8B%B1%EC%9D%98%EB%8B%A8%EA%B2%80</t>
-  </si>
-  <si>
-    <t>7조 5637억 146만</t>
-  </si>
-  <si>
-    <t>상급이다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B8%89%EC%9D%B4%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>7조 3720억 2210만</t>
-  </si>
-  <si>
-    <t>삐졌음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%90%EC%A1%8C%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>6조 9069억 7246만</t>
-  </si>
-  <si>
-    <t>성월야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EC%9B%94%EC%95%BC</t>
-  </si>
-  <si>
-    <t>6조 6783억 7144만</t>
-  </si>
-  <si>
-    <t>알른지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%A5%B8%EC%A7%80</t>
-  </si>
-  <si>
-    <t>6조 5725억 7031만</t>
-  </si>
-  <si>
-    <t>연평후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%ED%8F%89%ED%9B%84</t>
-  </si>
-  <si>
-    <t>6조 2525억 4645만</t>
-  </si>
-  <si>
     <t>핸슈님</t>
   </si>
   <si>
@@ -908,15 +899,6 @@
     <t>2640조 3289억 9968만</t>
   </si>
   <si>
-    <t>노루상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EB%A3%A8%EC%83%81</t>
-  </si>
-  <si>
-    <t>21조 152억 1979만</t>
-  </si>
-  <si>
     <t>김갑빠</t>
   </si>
   <si>
@@ -1004,7 +986,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>8604억 742만</t>
+    <t>8616억 2541만</t>
   </si>
   <si>
     <t>내이름은츈식</t>
@@ -1136,7 +1118,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%91%EA%B5%AC</t>
   </si>
   <si>
-    <t>41조 7861억 8048만</t>
+    <t>42조 2513억 375만</t>
   </si>
   <si>
     <t>mumu5</t>
@@ -1173,15 +1155,6 @@
   </si>
   <si>
     <t>8조 6504억 7197만</t>
-  </si>
-  <si>
-    <t>확률단속</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%95%EB%A5%A0%EB%8B%A8%EC%86%8D</t>
-  </si>
-  <si>
-    <t>7조 7023억 931만</t>
   </si>
   <si>
     <t>꼼웅</t>
@@ -2097,7 +2070,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2609,10 +2582,10 @@
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>142</v>
@@ -2641,7 +2614,7 @@
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>119</v>
@@ -2705,13 +2678,13 @@
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>119</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2722,25 +2695,25 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>159</v>
@@ -2769,7 +2742,7 @@
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>114</v>
@@ -2801,13 +2774,13 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -2818,25 +2791,25 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>172</v>
@@ -2865,10 +2838,10 @@
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>176</v>
@@ -2897,10 +2870,10 @@
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>180</v>
@@ -2929,10 +2902,10 @@
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>184</v>
@@ -2961,7 +2934,7 @@
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>114</v>
@@ -2993,10 +2966,10 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>192</v>
@@ -3005,40 +2978,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J28"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3067,7 +3008,6 @@
     <hyperlink ref="E26" r:id="rId25"/>
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3134,7 +3074,7 @@
         <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
@@ -3143,10 +3083,10 @@
         <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3160,13 +3100,13 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
@@ -3178,7 +3118,7 @@
         <v>99</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3192,13 +3132,13 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
@@ -3210,7 +3150,7 @@
         <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3224,25 +3164,25 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3256,13 +3196,13 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
@@ -3274,7 +3214,7 @@
         <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3288,13 +3228,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
@@ -3306,7 +3246,7 @@
         <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3320,13 +3260,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -3338,7 +3278,7 @@
         <v>119</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3352,13 +3292,13 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
@@ -3370,7 +3310,7 @@
         <v>114</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3384,13 +3324,13 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
@@ -3402,7 +3342,7 @@
         <v>119</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3416,13 +3356,13 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -3434,7 +3374,7 @@
         <v>114</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3448,13 +3388,13 @@
         <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
@@ -3466,7 +3406,7 @@
         <v>114</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3480,25 +3420,25 @@
         <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3512,13 +3452,13 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -3530,7 +3470,7 @@
         <v>114</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3544,13 +3484,13 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
@@ -3562,7 +3502,7 @@
         <v>114</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3576,13 +3516,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
@@ -3594,7 +3534,7 @@
         <v>114</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3608,13 +3548,13 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
@@ -3623,10 +3563,10 @@
         <v>109</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3640,13 +3580,13 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
@@ -3655,10 +3595,10 @@
         <v>78</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3672,13 +3612,13 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
@@ -3690,7 +3630,7 @@
         <v>114</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3701,16 +3641,16 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
@@ -3719,10 +3659,10 @@
         <v>93</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3736,13 +3676,13 @@
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
@@ -3751,10 +3691,10 @@
         <v>93</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3768,13 +3708,13 @@
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
@@ -3783,10 +3723,10 @@
         <v>109</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3797,16 +3737,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
@@ -3815,10 +3755,10 @@
         <v>133</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3832,13 +3772,13 @@
         <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
@@ -3847,10 +3787,10 @@
         <v>109</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3864,13 +3804,13 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
@@ -3879,10 +3819,10 @@
         <v>133</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3896,13 +3836,13 @@
         <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
@@ -3911,10 +3851,10 @@
         <v>133</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3928,13 +3868,13 @@
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -3946,7 +3886,7 @@
         <v>114</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3960,13 +3900,13 @@
         <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
@@ -3975,10 +3915,10 @@
         <v>98</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3989,16 +3929,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -4007,10 +3947,10 @@
         <v>133</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4021,16 +3961,16 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
@@ -4039,10 +3979,10 @@
         <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4053,16 +3993,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
@@ -4071,10 +4011,10 @@
         <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4120,7 +4060,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4179,7 +4119,7 @@
         <v>44</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>87</v>
@@ -4188,10 +4128,10 @@
         <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4205,13 +4145,13 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
@@ -4220,10 +4160,10 @@
         <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4237,25 +4177,25 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>119</v>
+        <v>167</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4269,25 +4209,25 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4301,25 +4241,25 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4333,25 +4273,25 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4365,25 +4305,25 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4397,13 +4337,13 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
@@ -4412,10 +4352,10 @@
         <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4429,25 +4369,25 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4461,25 +4401,25 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4493,25 +4433,25 @@
         <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>325</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4525,25 +4465,25 @@
         <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4557,64 +4497,32 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J15"/>
+  <autoFilter ref="A1:J14"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4629,7 +4537,6 @@
     <hyperlink ref="E12" r:id="rId11"/>
     <hyperlink ref="E13" r:id="rId12"/>
     <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4637,7 +4544,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4690,13 +4597,13 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
@@ -4705,10 +4612,10 @@
         <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4722,13 +4629,13 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
@@ -4740,7 +4647,7 @@
         <v>88</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4754,13 +4661,13 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
@@ -4772,7 +4679,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4786,13 +4693,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
@@ -4804,7 +4711,7 @@
         <v>79</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4818,13 +4725,13 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
@@ -4836,7 +4743,7 @@
         <v>73</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4850,13 +4757,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
@@ -4868,7 +4775,7 @@
         <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4882,13 +4789,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -4900,7 +4807,7 @@
         <v>79</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4914,13 +4821,13 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
@@ -4932,7 +4839,7 @@
         <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4946,13 +4853,13 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
@@ -4964,7 +4871,7 @@
         <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4978,13 +4885,13 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -4996,7 +4903,7 @@
         <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5010,13 +4917,13 @@
         <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
@@ -5028,7 +4935,7 @@
         <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5042,13 +4949,13 @@
         <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
@@ -5060,7 +4967,7 @@
         <v>104</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5074,13 +4981,13 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -5092,7 +4999,7 @@
         <v>114</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5106,13 +5013,13 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
@@ -5124,7 +5031,7 @@
         <v>114</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5138,13 +5045,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
@@ -5153,10 +5060,10 @@
         <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5170,25 +5077,25 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5202,64 +5109,32 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>171</v>
+        <v>262</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J19"/>
+  <autoFilter ref="A1:J18"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5278,7 +5153,6 @@
     <hyperlink ref="E16" r:id="rId15"/>
     <hyperlink ref="E17" r:id="rId16"/>
     <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5339,13 +5213,13 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
@@ -5357,7 +5231,7 @@
         <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5371,13 +5245,13 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
@@ -5389,7 +5263,7 @@
         <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5403,13 +5277,13 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
@@ -5421,7 +5295,7 @@
         <v>73</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5435,13 +5309,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
@@ -5453,7 +5327,7 @@
         <v>79</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5467,13 +5341,13 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
@@ -5485,7 +5359,7 @@
         <v>73</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5505,7 +5379,7 @@
         <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>87</v>
@@ -5517,7 +5391,7 @@
         <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5531,13 +5405,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -5549,7 +5423,7 @@
         <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5563,13 +5437,13 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
@@ -5581,7 +5455,7 @@
         <v>104</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5595,13 +5469,13 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
@@ -5613,7 +5487,7 @@
         <v>119</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5627,13 +5501,13 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -5645,7 +5519,7 @@
         <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5659,13 +5533,13 @@
         <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
@@ -5677,7 +5551,7 @@
         <v>79</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5691,13 +5565,13 @@
         <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
@@ -5709,7 +5583,7 @@
         <v>104</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5723,13 +5597,13 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -5741,7 +5615,7 @@
         <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5755,13 +5629,13 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
@@ -5773,7 +5647,7 @@
         <v>104</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5787,13 +5661,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
@@ -5805,7 +5679,7 @@
         <v>104</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5819,13 +5693,13 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
@@ -5837,7 +5711,7 @@
         <v>119</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5851,13 +5725,13 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
@@ -5869,7 +5743,7 @@
         <v>104</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5883,25 +5757,25 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>119</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5912,16 +5786,16 @@
         <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
@@ -5933,7 +5807,7 @@
         <v>104</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5947,13 +5821,13 @@
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
@@ -5965,7 +5839,7 @@
         <v>104</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5979,13 +5853,13 @@
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
@@ -5997,7 +5871,7 @@
         <v>119</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6008,16 +5882,16 @@
         <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
@@ -6029,7 +5903,7 @@
         <v>104</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6043,13 +5917,13 @@
         <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
@@ -6061,7 +5935,7 @@
         <v>119</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6075,13 +5949,13 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
@@ -6093,7 +5967,7 @@
         <v>119</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6107,13 +5981,13 @@
         <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
@@ -6125,7 +5999,7 @@
         <v>104</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6139,13 +6013,13 @@
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -6157,7 +6031,7 @@
         <v>99</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6171,13 +6045,13 @@
         <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
@@ -6189,7 +6063,7 @@
         <v>114</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6200,16 +6074,16 @@
         <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -6221,7 +6095,7 @@
         <v>114</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6232,16 +6106,16 @@
         <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
@@ -6253,7 +6127,7 @@
         <v>114</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
